--- a/engine/adib_study/ADIB_Valuation_Model_09092026.xlsx
+++ b/engine/adib_study/ADIB_Valuation_Model_09092026.xlsx
@@ -1193,9 +1193,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4">
-        <f> Dividend</f>
-        <v/>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>equals the Dividend</t>
+        </is>
       </c>
       <c r="C7" s="6">
         <f>'Balance Sheet'!C13</f>
@@ -1246,9 +1247,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4">
-        <f> NET FLOW TO SHAREHOLDERS</f>
-        <v/>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>equals the NET FLOW TO SHAREHOLDERS</t>
+        </is>
       </c>
       <c r="C9" s="6">
         <f>'Balance Sheet'!C15</f>
@@ -3476,7 +3478,7 @@
         </is>
       </c>
       <c r="B24" s="6">
-        <f>(H21*(1+'Assumptions'!$B$28)/('Assumptions'!$B$31-'Assumptions'!$B$28))*H5</f>
+        <f>(('Income Statement'!I14-'Assumptions'!$B$31*'Balance Sheet'!G10)*(1+'Assumptions'!$B$28)/('Assumptions'!$B$31-'Assumptions'!$B$28))*H5</f>
         <v/>
       </c>
     </row>

--- a/engine/adib_study/ADIB_Valuation_Model_09092026.xlsx
+++ b/engine/adib_study/ADIB_Valuation_Model_09092026.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ADIB-Egypt (EGX: ADIB) — valuation model, 2026-09-09</t>
+          <t>ADIB-Egypt (EGX: ADIB) — valuation model, 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>32.9134</v>
+        <v>38.5016</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>-0.114705</v>
+        <v>-0.112625</v>
       </c>
     </row>
     <row r="4">
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>41.4424</v>
+        <v>48.2747</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>0.114705</v>
+        <v>0.112625</v>
       </c>
     </row>
     <row r="5">
@@ -1993,10 +1993,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>28.7088</v>
+        <v>33.7101</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>-0.227799</v>
+        <v>-0.223057</v>
       </c>
     </row>
     <row r="6">
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>45.647</v>
+        <v>53.0662</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>0.227799</v>
+        <v>0.223057</v>
       </c>
     </row>
     <row r="7">
@@ -2019,10 +2019,10 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>29.9368</v>
+        <v>35.1134</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>-0.194768</v>
+        <v>-0.190714</v>
       </c>
     </row>
     <row r="8">
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>44.419</v>
+        <v>51.6629</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>0.194768</v>
+        <v>0.190714</v>
       </c>
     </row>
     <row r="9">
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>33.0317</v>
+        <v>37.8479</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>-0.111523</v>
+        <v>-0.12769</v>
       </c>
     </row>
     <row r="10">
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>41.8325</v>
+        <v>49.6443</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>0.125198</v>
+        <v>0.144191</v>
       </c>
     </row>
     <row r="11">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>31.445</v>
+        <v>35.8297</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>-0.154201</v>
+        <v>-0.174205</v>
       </c>
     </row>
     <row r="12">
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>45.0648</v>
+        <v>54.3876</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.212139</v>
+        <v>0.253513</v>
       </c>
     </row>
     <row r="13">
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>37.9935</v>
+        <v>44.895</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0.021937</v>
+        <v>0.034729</v>
       </c>
     </row>
     <row r="14">
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>36.4533</v>
+        <v>42.1011</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>-0.019491</v>
+        <v>-0.029663</v>
       </c>
     </row>
     <row r="16">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Egypt ten-year EGP government bond yield, 23.00%, the quote of 6 August 2026 held in engine/macro_path.py and already used by the PHDC, EGCH and PHAR cost-of-capital records. IT IS 34 DAYS OLD AGAINST THIS STUDY'S PRICING DATE AND THE HOUSE PATH'S OWN 14-DAY STALENESS RULE FLAGS IT AS STALE. A live re-source was attempted on 9 September 2026 down four routes and all four failed: the central bank's treasury-bond auction pages return 404, its auction API returns the site shell, the market-data pages render their yield tables in JavaScript, and the investing.com bond page returns 403. The level is carried, the staleness is declared here rather than buried, and the rate is sensitised by +/-200 basis points in section 1.9.</t>
+          <t>Egypt ten-year EGP government bond yield, 23.00%, the quote of 6 August 2026 held in the house macroeconomic path and already used by the PHDC, EGCH and PHAR cost-of-capital records. IT IS 34 DAYS OLD AGAINST THIS STUDY'S PRICING DATE AND THE HOUSE PATH'S OWN 14-DAY STALENESS RULE FLAGS IT AS STALE. A live re-source was attempted on 9 September 2026 down four routes and all four failed: the central bank's treasury-bond auction pages return 404, its auction API returns the site shell, the market-data pages render their yield tables in JavaScript, and the investing.com bond page returns 403. The level is carried, the staleness is declared here rather than buried, and the rate is sensitised by +/-200 basis points in section 1.9.</t>
         </is>
       </c>
     </row>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>Egypt sovereign credit-default-swap spread, 3.42%, mid-year (July 2026) vintage of the country default-spread dataset, Egypt row, "Sovereign CDS net of Swiss CDS". Netted out of the local-currency risk-free rate so that sovereign default risk is charged ONCE, inside the equity risk premium, and not twice [L-004]. engine/macro_path.py carries 3.41% for the same field from the same file; the one-basis-point difference is a rounding artefact and is immaterial.</t>
+          <t>Egypt sovereign credit-default-swap spread, 3.42%, mid-year (July 2026) vintage of the country default-spread dataset, Egypt row, "Sovereign CDS net of Swiss CDS". Netted out of the local-currency risk-free rate so that sovereign default risk is charged ONCE, inside the equity risk premium, and not twice. The house macroeconomic path carries 3.41% for the same field from the same file; the one-basis-point difference is a rounding artefact and is immaterial.</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>0.125</v>
+        <v>0.105</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
